--- a/Data/FlightPlan/FPL_08AUG26.xlsx
+++ b/Data/FlightPlan/FPL_08AUG26.xlsx
@@ -755,6 +755,9 @@
     <t>17:35</t>
   </si>
   <si>
+    <t>20:24</t>
+  </si>
+  <si>
     <t>22:25</t>
   </si>
   <si>
@@ -995,6 +998,9 @@
     <t>01:10</t>
   </si>
   <si>
+    <t>01:30</t>
+  </si>
+  <si>
     <t>VN-A580</t>
   </si>
   <si>
@@ -1127,33 +1133,36 @@
     <t>SAI</t>
   </si>
   <si>
+    <t>20:01</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
     <t>18:55</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>13:02</t>
-  </si>
-  <si>
     <t>20:40</t>
   </si>
   <si>
@@ -1205,522 +1214,528 @@
     <t>21:05</t>
   </si>
   <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>20:31</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
+    <t>18:18</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>09:46</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:38</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:12</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>20:17</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>00:31</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>18:33</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>18:42</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>10:21</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>06:58</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>17:49</t>
+  </si>
+  <si>
+    <t>21:01</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>12:14</t>
+  </si>
+  <si>
+    <t>20:21</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>17:21</t>
+  </si>
+  <si>
+    <t>19:51</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>20:31</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>15:46</t>
-  </si>
-  <si>
-    <t>18:18</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>09:46</t>
-  </si>
-  <si>
-    <t>14:46</t>
-  </si>
-  <si>
-    <t>VDH</t>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>15:42</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>08:17</t>
+  </si>
+  <si>
+    <t>15:14</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>18:34</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>20:08</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>18:57</t>
   </si>
   <si>
     <t>19:35</t>
   </si>
   <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:38</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>16:19</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:12</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:34</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>00:31</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>11:28</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>18:33</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:03</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>14:58</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>18:42</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>14:51</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:36</t>
-  </si>
-  <si>
-    <t>13:59</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>07:42</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>14:56</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>06:58</t>
-  </si>
-  <si>
-    <t>09:06</t>
-  </si>
-  <si>
-    <t>17:49</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>12:14</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>17:21</t>
-  </si>
-  <si>
-    <t>19:51</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>00:02</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>13:52</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>14:52</t>
-  </si>
-  <si>
-    <t>18:46</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>13:12</t>
-  </si>
-  <si>
-    <t>15:42</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>16:56</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>15:51</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>08:17</t>
-  </si>
-  <si>
-    <t>15:14</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>18:34</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>20:08</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>18:57</t>
-  </si>
-  <si>
     <t>22:05</t>
   </si>
   <si>
@@ -1790,7 +1805,7 @@
     <t>13:51</t>
   </si>
   <si>
-    <t>20:01</t>
+    <t>20:03</t>
   </si>
   <si>
     <t>VN-A810</t>
@@ -1850,7 +1865,7 @@
     <t>Total Record(s): 456</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 08, 2026 18:06</t>
+    <t xml:space="preserve">Generated on  Aug 08, 2026 18:18</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5617,7 +5632,9 @@
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>248</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
@@ -5646,7 +5663,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5679,13 +5696,13 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>73</v>
@@ -5694,12 +5711,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5714,7 +5731,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5726,15 +5743,15 @@
         <v>162</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5749,7 +5766,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5764,7 +5781,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5782,7 +5799,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5791,10 +5808,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>157</v>
@@ -5830,7 +5847,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5842,7 +5859,7 @@
         <v>241</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>43</v>
@@ -5850,7 +5867,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5865,7 +5882,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5877,7 +5894,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>238</v>
@@ -5900,7 +5917,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5915,7 +5932,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5933,7 +5950,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5966,7 +5983,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5975,10 +5992,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>217</v>
@@ -6014,7 +6031,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -6026,7 +6043,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>40</v>
@@ -6034,7 +6051,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6049,7 +6066,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6069,7 +6086,7 @@
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6084,7 +6101,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6099,14 +6116,14 @@
         <v>28</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="K124" s="7">
         <v>149</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6121,7 +6138,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6133,10 +6150,10 @@
         <v>166</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -6165,11 +6182,11 @@
         <v>21</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6178,10 +6195,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>70</v>
@@ -6189,7 +6206,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -6219,7 +6236,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6234,12 +6251,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6254,7 +6271,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6269,12 +6286,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6289,7 +6306,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6304,12 +6321,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6324,7 +6341,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6336,7 +6353,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>173</v>
@@ -6359,7 +6376,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6379,7 +6396,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6394,7 +6411,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6409,7 +6426,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -6442,7 +6459,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6454,15 +6471,15 @@
         <v>56</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6477,7 +6494,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6489,7 +6506,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>125</v>
@@ -6525,7 +6542,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6537,15 +6554,15 @@
         <v>156</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6560,7 +6577,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6569,10 +6586,10 @@
         <v>156</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>45</v>
@@ -6595,13 +6612,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>156</v>
@@ -6615,7 +6632,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6630,7 +6647,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6645,7 +6662,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6678,7 +6695,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6698,7 +6715,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6713,7 +6730,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6728,12 +6745,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6748,7 +6765,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6768,7 +6785,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6783,7 +6800,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6801,11 +6818,11 @@
         <v>227</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6820,7 +6837,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6842,7 +6859,7 @@
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6857,7 +6874,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6872,7 +6889,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6890,7 +6907,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6938,7 +6955,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6950,15 +6967,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6973,7 +6990,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6988,12 +7005,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7008,7 +7025,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7023,12 +7040,12 @@
         <v>160</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7043,7 +7060,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7063,7 +7080,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7078,7 +7095,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7087,18 +7104,18 @@
         <v>73</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>176</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7113,13 +7130,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>73</v>
@@ -7128,7 +7145,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -7161,13 +7178,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>73</v>
@@ -7176,12 +7193,12 @@
         <v>160</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7196,7 +7213,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7216,7 +7233,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7231,7 +7248,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7246,7 +7263,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7279,7 +7296,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7291,7 +7308,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>183</v>
@@ -7299,7 +7316,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7314,7 +7331,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7329,7 +7346,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7349,7 +7366,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7361,14 +7378,16 @@
         <v>56</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>329</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="6"/>
@@ -7397,7 +7416,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7412,12 +7431,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7432,7 +7451,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7452,7 +7471,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7467,7 +7486,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7476,13 +7495,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="I169" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="K169" s="7">
         <v>30</v>
@@ -7504,13 +7523,13 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>17</v>
@@ -7526,7 +7545,7 @@
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7556,7 +7575,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7568,7 +7587,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>59</v>
@@ -7576,7 +7595,7 @@
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7591,7 +7610,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7603,7 +7622,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>183</v>
@@ -7611,7 +7630,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7626,7 +7645,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7644,11 +7663,11 @@
         <v>235</v>
       </c>
       <c t="s" r="K174" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7663,7 +7682,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7681,7 +7700,7 @@
         <v>198</v>
       </c>
       <c t="s" r="K175" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
@@ -7700,7 +7719,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7709,13 +7728,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="K176" s="7">
         <v>80</v>
@@ -7737,13 +7756,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>17</v>
@@ -7752,14 +7771,14 @@
         <v>48</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="K177" s="7">
         <v>208</v>
       </c>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7789,7 +7808,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7801,7 +7820,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>112</v>
@@ -7824,7 +7843,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7836,7 +7855,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>130</v>
@@ -7859,7 +7878,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7871,7 +7890,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>238</v>
@@ -7894,7 +7913,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7909,7 +7928,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7927,7 +7946,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7939,10 +7958,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7960,7 +7979,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7972,7 +7991,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>220</v>
@@ -8008,27 +8027,27 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8043,7 +8062,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8052,7 +8071,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>212</v>
@@ -8063,7 +8082,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8078,27 +8097,27 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8113,7 +8132,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8125,7 +8144,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>36</v>
@@ -8161,7 +8180,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8173,7 +8192,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>152</v>
@@ -8181,7 +8200,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8196,7 +8215,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8216,7 +8235,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8231,7 +8250,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8243,7 +8262,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>212</v>
@@ -8266,7 +8285,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8278,17 +8297,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="K194" s="7">
         <v>195</v>
       </c>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8303,7 +8322,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8325,7 +8344,7 @@
       </c>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8340,7 +8359,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8355,14 +8374,14 @@
         <v>116</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="K196" s="7">
         <v>48</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8392,7 +8411,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8404,7 +8423,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>168</v>
@@ -8412,7 +8431,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8427,7 +8446,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8447,7 +8466,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8462,7 +8481,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8477,12 +8496,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8497,7 +8516,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8509,10 +8528,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="K201" s="7">
         <v>63</v>
@@ -8534,7 +8553,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8549,14 +8568,14 @@
         <v>129</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K202" s="7">
         <v>20</v>
       </c>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8571,7 +8590,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8580,7 +8599,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>198</v>
@@ -8593,7 +8612,7 @@
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8608,29 +8627,29 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="K204" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8645,7 +8664,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8654,20 +8673,20 @@
         <v>73</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="K205" s="7">
         <v>69</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8682,25 +8701,25 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="K206" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
@@ -8734,7 +8753,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8769,7 +8788,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8789,7 +8808,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8804,7 +8823,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8813,10 +8832,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>19</v>
@@ -8824,7 +8843,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8839,13 +8858,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>73</v>
@@ -8874,7 +8893,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8909,7 +8928,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8924,7 +8943,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8942,7 +8961,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8951,13 +8970,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I214" s="7">
         <v>184</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8975,13 +8994,13 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>73</v>
@@ -8990,7 +9009,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -9023,7 +9042,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9043,7 +9062,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9058,7 +9077,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9073,12 +9092,12 @@
         <v>222</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9093,7 +9112,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9102,18 +9121,18 @@
         <v>73</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9128,13 +9147,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>73</v>
@@ -9146,7 +9165,7 @@
         <v>195</v>
       </c>
       <c t="s" r="K220" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
@@ -9165,7 +9184,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9174,7 +9193,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>197</v>
@@ -9187,7 +9206,7 @@
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9202,13 +9221,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>73</v>
@@ -9217,10 +9236,10 @@
         <v>216</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="K222" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
@@ -9239,7 +9258,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9254,7 +9273,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>89</v>
@@ -9276,7 +9295,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9288,13 +9307,13 @@
         <v>73</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>31</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
@@ -9328,7 +9347,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9340,7 +9359,7 @@
         <v>241</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>176</v>
@@ -9363,7 +9382,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9413,7 +9432,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9433,7 +9452,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9448,7 +9467,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9460,15 +9479,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9483,7 +9502,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9492,10 +9511,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>142</v>
@@ -9503,7 +9522,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9518,13 +9537,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>73</v>
@@ -9536,11 +9555,11 @@
         <v>183</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9555,7 +9574,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9567,17 +9586,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>246</v>
       </c>
       <c t="s" r="K233" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9592,7 +9611,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9629,7 +9648,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9641,17 +9660,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c t="s" r="K235" s="7">
-        <v>208</v>
+        <v>48</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>289</v>
+        <v>401</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9666,7 +9685,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9684,11 +9703,11 @@
         <v>83</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>110</v>
+        <v>203</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9703,7 +9722,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9721,11 +9740,11 @@
         <v>151</v>
       </c>
       <c t="s" r="K237" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>126</v>
+        <v>403</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9755,7 +9774,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9767,15 +9786,15 @@
         <v>79</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9790,7 +9809,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9810,7 +9829,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9825,7 +9844,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9834,10 +9853,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>130</v>
@@ -9860,13 +9879,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>57</v>
@@ -9875,12 +9894,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9895,7 +9914,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9904,7 +9923,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>102</v>
@@ -9915,7 +9934,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9930,19 +9949,19 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>179</v>
@@ -9978,7 +9997,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9998,7 +10017,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -10013,7 +10032,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10025,10 +10044,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -10048,7 +10067,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10060,15 +10079,15 @@
         <v>156</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10083,7 +10102,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10103,7 +10122,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10133,7 +10152,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10148,12 +10167,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10168,7 +10187,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10180,10 +10199,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -10203,7 +10222,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10223,7 +10242,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10238,7 +10257,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10273,7 +10292,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10282,20 +10301,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="K255" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>416</v>
+        <v>355</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10310,13 +10329,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
@@ -10347,7 +10366,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10362,14 +10381,14 @@
         <v>123</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="K257" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10399,19 +10418,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
+        <v>422</v>
+      </c>
+      <c r="F259" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G259" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H259" s="8">
         <v>419</v>
       </c>
-      <c r="F259" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G259" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H259" s="8">
-        <v>415</v>
-      </c>
       <c t="s" r="I259" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>85</v>
@@ -10419,7 +10438,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10434,13 +10453,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
+        <v>422</v>
+      </c>
+      <c r="F260" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G260" s="8">
         <v>419</v>
-      </c>
-      <c r="F260" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G260" s="8">
-        <v>415</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
@@ -10454,7 +10473,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10469,7 +10488,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10478,20 +10497,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c t="s" r="K261" s="7">
         <v>160</v>
       </c>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10506,29 +10525,29 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c t="s" r="K262" s="7">
         <v>212</v>
       </c>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10543,7 +10562,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10552,13 +10571,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10578,13 +10597,13 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>17</v>
@@ -10615,7 +10634,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10630,10 +10649,10 @@
         <v>239</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="K265" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
@@ -10652,7 +10671,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10664,10 +10683,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10700,7 +10719,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10709,18 +10728,18 @@
         <v>73</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10735,13 +10754,13 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>73</v>
@@ -10755,7 +10774,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10770,7 +10789,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10782,7 +10801,7 @@
         <v>145</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>19</v>
@@ -10790,7 +10809,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10805,7 +10824,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10825,7 +10844,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10840,7 +10859,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10873,7 +10892,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10882,7 +10901,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>107</v>
@@ -10906,19 +10925,19 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>50</v>
@@ -10954,7 +10973,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10963,18 +10982,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10989,13 +11008,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>17</v>
@@ -11024,7 +11043,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -11033,7 +11052,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>193</v>
@@ -11044,7 +11063,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11059,13 +11078,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -11079,7 +11098,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11094,7 +11113,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11103,10 +11122,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>26</v>
@@ -11114,7 +11133,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11129,13 +11148,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
@@ -11177,7 +11196,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11197,7 +11216,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11212,7 +11231,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11221,18 +11240,18 @@
         <v>135</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11247,13 +11266,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>135</v>
@@ -11267,7 +11286,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11282,7 +11301,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11302,7 +11321,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11317,7 +11336,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11336,7 +11355,9 @@
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
-      <c r="M287" s="7"/>
+      <c t="s" r="M287" s="7">
+        <v>444</v>
+      </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
       <c t="s" r="A288" s="6">
@@ -11350,7 +11371,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11362,10 +11383,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11398,7 +11419,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11413,12 +11434,12 @@
         <v>152</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11433,7 +11454,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11442,7 +11463,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>198</v>
@@ -11453,7 +11474,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11468,19 +11489,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>54</v>
@@ -11516,7 +11537,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11528,15 +11549,15 @@
         <v>115</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11551,7 +11572,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11563,7 +11584,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>160</v>
@@ -11571,7 +11592,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11586,7 +11607,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11601,12 +11622,12 @@
         <v>212</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11621,7 +11642,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11654,7 +11675,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11702,7 +11723,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11717,14 +11738,14 @@
         <v>39</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11739,7 +11760,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11751,17 +11772,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>173</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11776,7 +11797,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11791,14 +11812,14 @@
         <v>244</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="K302" s="7">
         <v>197</v>
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11813,7 +11834,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11828,10 +11849,10 @@
         <v>208</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="K303" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
@@ -11865,7 +11886,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11877,15 +11898,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11900,7 +11921,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11909,10 +11930,10 @@
         <v>21</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>39</v>
@@ -11935,27 +11956,27 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11970,7 +11991,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11982,7 +12003,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>19</v>
@@ -12005,7 +12026,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12017,7 +12038,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>227</v>
@@ -12025,7 +12046,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12040,7 +12061,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -12060,7 +12081,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -12075,7 +12096,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12097,7 +12118,7 @@
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12112,7 +12133,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -12124,17 +12145,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="K312" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12164,7 +12185,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12179,12 +12200,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12199,7 +12220,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12219,7 +12240,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12234,7 +12255,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12243,10 +12264,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>41</v>
@@ -12254,7 +12275,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12269,29 +12290,29 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12306,7 +12327,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12315,10 +12336,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>175</v>
@@ -12328,7 +12349,7 @@
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12343,13 +12364,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
@@ -12358,14 +12379,14 @@
         <v>103</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="K319" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12380,7 +12401,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12392,10 +12413,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="K320" s="7">
         <v>44</v>
@@ -12417,7 +12438,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12435,11 +12456,11 @@
         <v>46</v>
       </c>
       <c t="s" r="K321" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12454,7 +12475,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12466,10 +12487,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12487,7 +12508,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12499,10 +12520,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12535,7 +12556,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12544,7 +12565,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>209</v>
@@ -12555,7 +12576,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12570,27 +12591,27 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12605,7 +12626,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12614,18 +12635,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12640,13 +12661,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>17</v>
@@ -12675,7 +12696,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12690,14 +12711,14 @@
         <v>43</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="K329" s="7">
         <v>132</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12712,7 +12733,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12724,7 +12745,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>215</v>
@@ -12734,7 +12755,7 @@
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12749,7 +12770,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12764,14 +12785,14 @@
         <v>200</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="K331" s="7">
         <v>46</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12786,7 +12807,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12823,7 +12844,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12845,7 +12866,7 @@
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>474</v>
+        <v>329</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12875,7 +12896,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12887,7 +12908,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>220</v>
@@ -12895,7 +12916,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12910,7 +12931,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12945,7 +12966,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12965,7 +12986,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12980,7 +13001,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -13013,7 +13034,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -13061,7 +13082,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13081,7 +13102,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13096,7 +13117,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13108,7 +13129,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>193</v>
@@ -13116,7 +13137,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13131,7 +13152,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -13143,15 +13164,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13166,7 +13187,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -13181,12 +13202,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13201,7 +13222,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13236,7 +13257,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13245,17 +13266,19 @@
         <v>73</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I346" s="7">
         <v>216</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
-      <c r="M346" s="7"/>
+      <c t="s" r="M346" s="7">
+        <v>149</v>
+      </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
@@ -13269,13 +13292,13 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>73</v>
@@ -13284,7 +13307,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -13317,7 +13340,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13332,12 +13355,12 @@
         <v>94</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13352,7 +13375,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13367,12 +13390,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13387,7 +13410,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13399,7 +13422,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>163</v>
@@ -13407,7 +13430,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13422,7 +13445,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13442,7 +13465,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13457,7 +13480,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13466,10 +13489,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>215</v>
@@ -13477,7 +13500,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13492,13 +13515,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>73</v>
@@ -13507,7 +13530,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c t="s" r="K354" s="7">
         <v>80</v>
@@ -13529,7 +13552,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13538,7 +13561,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>149</v>
@@ -13551,7 +13574,7 @@
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13566,13 +13589,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>73</v>
@@ -13581,14 +13604,14 @@
         <v>91</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c t="s" r="K356" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13618,7 +13641,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13633,12 +13656,12 @@
         <v>209</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13653,7 +13676,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13662,18 +13685,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13688,27 +13711,27 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13723,7 +13746,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13758,7 +13781,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13770,7 +13793,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>216</v>
@@ -13793,7 +13816,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13802,10 +13825,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>184</v>
@@ -13815,7 +13838,7 @@
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13830,13 +13853,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>17</v>
@@ -13848,7 +13871,7 @@
         <v>82</v>
       </c>
       <c t="s" r="K364" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
@@ -13882,7 +13905,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13902,7 +13925,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13917,7 +13940,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13932,12 +13955,12 @@
         <v>190</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13952,7 +13975,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13964,7 +13987,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>183</v>
@@ -13972,7 +13995,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13987,7 +14010,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13999,7 +14022,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>195</v>
@@ -14007,7 +14030,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -14022,7 +14045,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -14040,7 +14063,7 @@
         <v>213</v>
       </c>
       <c t="s" r="K370" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
@@ -14059,7 +14082,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -14074,7 +14097,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="K371" s="7">
         <v>116</v>
@@ -14111,7 +14134,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14131,7 +14154,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14146,7 +14169,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14158,15 +14181,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14181,7 +14204,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14193,15 +14216,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14216,7 +14239,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -14228,7 +14251,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>163</v>
@@ -14236,7 +14259,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14251,7 +14274,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14271,7 +14294,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14286,7 +14309,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14298,14 +14321,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
-      <c r="M378" s="7"/>
+      <c t="s" r="M378" s="7">
+        <v>507</v>
+      </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
@@ -14319,7 +14344,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14328,13 +14353,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -14352,22 +14377,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -14400,7 +14425,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14412,15 +14437,15 @@
         <v>188</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14435,7 +14460,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -14450,12 +14475,12 @@
         <v>163</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14470,7 +14495,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -14505,7 +14530,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14517,14 +14542,16 @@
         <v>73</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
-      <c r="M385" s="7"/>
+      <c t="s" r="M385" s="7">
+        <v>514</v>
+      </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
@@ -14538,7 +14565,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14553,14 +14580,14 @@
         <v>138</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="K386" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14575,7 +14602,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14587,7 +14614,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>110</v>
@@ -14597,7 +14624,7 @@
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14627,7 +14654,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14636,10 +14663,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>168</v>
@@ -14647,7 +14674,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14662,13 +14689,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>17</v>
@@ -14682,7 +14709,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14697,7 +14724,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14706,18 +14733,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14732,29 +14759,29 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>163</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14769,7 +14796,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14791,7 +14818,7 @@
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14806,7 +14833,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14821,7 +14848,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="K394" s="7">
         <v>133</v>
@@ -14843,7 +14870,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -14865,7 +14892,7 @@
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14895,7 +14922,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14910,12 +14937,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14930,7 +14957,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14950,7 +14977,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14965,7 +14992,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14974,7 +15001,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>20</v>
@@ -14983,11 +15010,11 @@
         <v>177</v>
       </c>
       <c t="s" r="K399" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -15002,19 +15029,19 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>184</v>
@@ -15024,7 +15051,7 @@
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -15039,7 +15066,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -15048,13 +15075,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>186</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>398</v>
+        <v>526</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -15072,22 +15099,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -15120,7 +15147,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15132,7 +15159,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>221</v>
@@ -15140,7 +15167,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15155,7 +15182,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15170,12 +15197,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15190,7 +15217,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15202,7 +15229,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>103</v>
@@ -15210,7 +15237,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15225,7 +15252,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -15237,7 +15264,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>80</v>
@@ -15277,7 +15304,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -15312,7 +15339,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -15324,15 +15351,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15347,7 +15374,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15359,7 +15386,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>244</v>
@@ -15382,7 +15409,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -15404,7 +15431,7 @@
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15419,7 +15446,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15428,7 +15455,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>238</v>
@@ -15439,7 +15466,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>529</v>
+        <v>316</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15454,22 +15481,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -15502,7 +15529,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15522,7 +15549,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15537,7 +15564,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15549,15 +15576,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15572,7 +15599,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15584,15 +15611,15 @@
         <v>156</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15607,7 +15634,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -15642,7 +15669,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -15657,7 +15684,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -15677,7 +15704,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15710,7 +15737,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15719,10 +15746,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>18</v>
@@ -15758,7 +15785,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15773,12 +15800,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15793,7 +15820,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15808,14 +15835,14 @@
         <v>233</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c t="s" r="K425" s="7">
         <v>183</v>
       </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15830,7 +15857,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15850,7 +15877,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15865,7 +15892,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15877,7 +15904,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>208</v>
@@ -15898,7 +15925,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15907,13 +15934,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15931,22 +15958,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -15979,7 +16006,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15994,12 +16021,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -16014,7 +16041,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -16026,7 +16053,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>19</v>
@@ -16034,7 +16061,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -16049,7 +16076,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -16058,7 +16085,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>43</v>
@@ -16069,7 +16096,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -16084,13 +16111,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>17</v>
@@ -16119,7 +16146,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -16134,7 +16161,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -16152,7 +16179,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -16200,7 +16227,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -16220,7 +16247,7 @@
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -16235,7 +16262,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -16270,7 +16297,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -16279,7 +16306,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>227</v>
@@ -16290,7 +16317,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16305,13 +16332,13 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
@@ -16324,7 +16351,9 @@
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
-      <c r="M441" s="7"/>
+      <c t="s" r="M441" s="7">
+        <v>46</v>
+      </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
       <c t="s" r="A442" s="6">
@@ -16338,7 +16367,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -16386,7 +16415,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -16401,12 +16430,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16421,7 +16450,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16456,7 +16485,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16468,17 +16497,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16493,7 +16522,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -16515,7 +16544,7 @@
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>48</v>
+        <v>356</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16545,7 +16574,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -16557,7 +16586,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>159</v>
@@ -16565,7 +16594,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16580,7 +16609,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -16628,7 +16657,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16643,12 +16672,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16663,7 +16692,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16678,12 +16707,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16698,7 +16727,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16710,7 +16739,7 @@
         <v>145</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>211</v>
@@ -16718,7 +16747,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16733,7 +16762,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16745,7 +16774,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>132</v>
@@ -16753,7 +16782,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16768,7 +16797,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -16803,7 +16832,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16818,7 +16847,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -16836,7 +16865,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
@@ -16869,7 +16898,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -16917,7 +16946,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -16937,7 +16966,7 @@
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
       <c t="s" r="M461" s="7">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
@@ -16952,7 +16981,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
@@ -16964,7 +16993,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J462" s="7">
         <v>191</v>
@@ -16972,7 +17001,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16987,7 +17016,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F463" s="7">
         <v>320</v>
@@ -16999,10 +17028,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -17022,7 +17051,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F464" s="7">
         <v>320</v>
@@ -17037,14 +17066,14 @@
         <v>63</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="K464" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -17059,7 +17088,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F465" s="7">
         <v>320</v>
@@ -17071,7 +17100,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>133</v>
@@ -17081,7 +17110,7 @@
       </c>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -17096,7 +17125,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F466" s="7">
         <v>320</v>
@@ -17111,14 +17140,14 @@
         <v>247</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c t="s" r="K466" s="7">
         <v>137</v>
       </c>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -17133,7 +17162,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F467" s="7">
         <v>320</v>
@@ -17145,17 +17174,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c t="s" r="K467" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -17185,7 +17214,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -17197,7 +17226,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>222</v>
@@ -17205,7 +17234,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -17220,7 +17249,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -17240,7 +17269,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17255,7 +17284,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -17267,13 +17296,13 @@
         <v>57</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>242</v>
       </c>
       <c t="s" r="K471" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
@@ -17292,7 +17321,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -17304,17 +17333,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>20</v>
       </c>
       <c t="s" r="K472" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -17329,7 +17358,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
@@ -17344,7 +17373,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="K473" s="7">
         <v>45</v>
@@ -17366,7 +17395,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -17381,10 +17410,10 @@
         <v>213</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="K474" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
@@ -17403,7 +17432,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -17412,13 +17441,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>474</v>
+        <v>329</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -17436,19 +17465,19 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c t="s" r="J476" s="7">
         <v>154</v>
@@ -17484,7 +17513,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -17499,12 +17528,12 @@
         <v>209</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -17519,7 +17548,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -17539,7 +17568,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17554,7 +17583,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -17566,7 +17595,7 @@
         <v>241</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J480" s="7">
         <v>175</v>
@@ -17589,7 +17618,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -17601,7 +17630,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>198</v>
@@ -17624,7 +17653,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -17644,7 +17673,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17659,7 +17688,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -17671,7 +17700,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J483" s="7">
         <v>121</v>
@@ -17692,7 +17721,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
@@ -17707,7 +17736,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -17740,7 +17769,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -17760,7 +17789,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -17775,7 +17804,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
@@ -17790,7 +17819,7 @@
         <v>224</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -17810,7 +17839,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -17830,7 +17859,7 @@
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -17845,7 +17874,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
@@ -17860,14 +17889,14 @@
         <v>147</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c t="s" r="K489" s="7">
-        <v>416</v>
+        <v>574</v>
       </c>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -17882,7 +17911,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -17894,17 +17923,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c t="s" r="K490" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L490" s="7"/>
       <c t="s" r="M490" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -17934,7 +17963,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -17949,12 +17978,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
       <c t="s" r="M492" s="7">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -17969,7 +17998,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
@@ -17978,10 +18007,10 @@
         <v>135</v>
       </c>
       <c t="s" r="H493" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c t="s" r="J493" s="7">
         <v>246</v>
@@ -18004,13 +18033,13 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G494" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="H494" s="8">
         <v>135</v>
@@ -18024,7 +18053,7 @@
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -18039,7 +18068,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F495" s="7">
         <v>321</v>
@@ -18054,12 +18083,12 @@
         <v>206</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
       <c t="s" r="M495" s="7">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="496" ht="14.25" customHeight="1">
@@ -18074,7 +18103,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F496" s="7">
         <v>321</v>
@@ -18086,7 +18115,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c t="s" r="J496" s="7">
         <v>202</v>
@@ -18107,7 +18136,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F497" s="7">
         <v>321</v>
@@ -18122,7 +18151,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J497" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
@@ -18155,7 +18184,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -18170,7 +18199,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J499" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
@@ -18190,7 +18219,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F500" s="7">
         <v>320</v>
@@ -18205,7 +18234,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J500" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
@@ -18225,7 +18254,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F501" s="7">
         <v>320</v>
@@ -18245,7 +18274,7 @@
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
       <c t="s" r="M501" s="7">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="502" ht="14.25" customHeight="1">
@@ -18260,7 +18289,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F502" s="7">
         <v>320</v>
@@ -18275,12 +18304,12 @@
         <v>227</v>
       </c>
       <c t="s" r="J502" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
       <c t="s" r="M502" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="503" ht="14.25" customHeight="1">
@@ -18295,7 +18324,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -18310,7 +18339,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
@@ -18328,7 +18357,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F504" s="7">
         <v>320</v>
@@ -18343,7 +18372,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J504" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
@@ -18376,7 +18405,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -18385,10 +18414,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H506" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J506" s="7">
         <v>195</v>
@@ -18411,27 +18440,27 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F507" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G507" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="H507" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I507" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J507" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
       <c t="s" r="M507" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="508" ht="14.25" customHeight="1">
@@ -18446,7 +18475,7 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F508" s="7">
         <v>321</v>
@@ -18455,7 +18484,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H508" s="8">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c t="s" r="I508" s="7">
         <v>107</v>
@@ -18479,22 +18508,22 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="F509" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G509" s="8">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c t="s" r="H509" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I509" s="7">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c t="s" r="J509" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
@@ -18527,7 +18556,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F511" s="7">
         <v>321</v>
@@ -18539,7 +18568,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c t="s" r="J511" s="7">
         <v>152</v>
@@ -18547,7 +18576,7 @@
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
       <c t="s" r="M511" s="7">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="512" ht="14.25" customHeight="1">
@@ -18562,7 +18591,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F512" s="7">
         <v>321</v>
@@ -18577,12 +18606,12 @@
         <v>193</v>
       </c>
       <c t="s" r="J512" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
       <c t="s" r="M512" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="513" ht="14.25" customHeight="1">
@@ -18597,7 +18626,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F513" s="7">
         <v>321</v>
@@ -18612,12 +18641,12 @@
         <v>216</v>
       </c>
       <c t="s" r="J513" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
       <c t="s" r="M513" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="514" ht="14.25" customHeight="1">
@@ -18632,7 +18661,7 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F514" s="7">
         <v>321</v>
@@ -18644,7 +18673,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I514" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J514" s="7">
         <v>35</v>
@@ -18680,7 +18709,7 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F516" s="7">
         <v>321</v>
@@ -18695,12 +18724,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
       <c t="s" r="M516" s="7">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -18715,7 +18744,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F517" s="7">
         <v>321</v>
@@ -18727,7 +18756,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I517" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J517" s="7">
         <v>212</v>
@@ -18735,7 +18764,7 @@
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -18750,7 +18779,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F518" s="7">
         <v>321</v>
@@ -18785,7 +18814,7 @@
       </c>
       <c r="D519" s="7"/>
       <c t="s" r="E519" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F519" s="7">
         <v>321</v>
@@ -18805,7 +18834,7 @@
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
       <c t="s" r="M519" s="7">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="520" ht="15" customHeight="1">
@@ -18820,7 +18849,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F520" s="7">
         <v>321</v>
@@ -18842,7 +18871,7 @@
       </c>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -18857,7 +18886,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F521" s="7">
         <v>321</v>
@@ -18875,7 +18904,7 @@
         <v>139</v>
       </c>
       <c t="s" r="K521" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L521" s="7"/>
       <c t="s" r="M521" s="7">
@@ -18909,7 +18938,7 @@
       </c>
       <c r="D523" s="7"/>
       <c t="s" r="E523" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F523" s="7">
         <v>320</v>
@@ -18929,7 +18958,7 @@
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
       <c t="s" r="M523" s="7">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="524" ht="14.25" customHeight="1">
@@ -18944,7 +18973,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F524" s="7">
         <v>320</v>
@@ -18956,10 +18985,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I524" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J524" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
@@ -18979,7 +19008,7 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F525" s="7">
         <v>320</v>
@@ -18991,7 +19020,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I525" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J525" s="7">
         <v>40</v>
@@ -18999,7 +19028,7 @@
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
       <c t="s" r="M525" s="7">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="526" ht="14.25" customHeight="1">
@@ -19014,7 +19043,7 @@
       </c>
       <c r="D526" s="7"/>
       <c t="s" r="E526" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F526" s="7">
         <v>320</v>
@@ -19026,15 +19055,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I526" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J526" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K526" s="7"/>
       <c r="L526" s="7"/>
       <c t="s" r="M526" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="527" ht="14.25" customHeight="1">
@@ -19049,7 +19078,7 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F527" s="7">
         <v>320</v>
@@ -19064,12 +19093,12 @@
         <v>215</v>
       </c>
       <c t="s" r="J527" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
       <c t="s" r="M527" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="528" ht="14.25" customHeight="1">
@@ -19084,7 +19113,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F528" s="7">
         <v>320</v>
@@ -19096,10 +19125,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I528" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J528" s="7">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
@@ -19132,27 +19161,27 @@
       </c>
       <c r="D530" s="7"/>
       <c t="s" r="E530" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F530" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G530" s="8">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c t="s" r="H530" s="8">
         <v>79</v>
       </c>
       <c t="s" r="I530" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c t="s" r="J530" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
       <c t="s" r="M530" s="7">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="531" ht="14.25" customHeight="1">
@@ -19167,7 +19196,7 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
@@ -19182,12 +19211,12 @@
         <v>173</v>
       </c>
       <c t="s" r="J531" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
       <c t="s" r="M531" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="532" ht="14.25" customHeight="1">
@@ -19202,7 +19231,7 @@
       </c>
       <c r="D532" s="7"/>
       <c t="s" r="E532" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F532" s="7">
         <v>330</v>
@@ -19211,10 +19240,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H532" s="8">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c t="s" r="I532" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J532" s="7">
         <v>119</v>
@@ -19224,7 +19253,7 @@
       </c>
       <c r="L532" s="7"/>
       <c t="s" r="M532" s="7">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="533" ht="14.25" customHeight="1">
@@ -19239,13 +19268,13 @@
       </c>
       <c r="D533" s="7"/>
       <c t="s" r="E533" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F533" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G533" s="8">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c t="s" r="H533" s="8">
         <v>57</v>
@@ -19287,7 +19316,7 @@
       </c>
       <c r="D535" s="7"/>
       <c t="s" r="E535" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F535" s="7">
         <v>330</v>
@@ -19296,18 +19325,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H535" s="8">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c t="s" r="I535" s="7">
         <v>220</v>
       </c>
       <c t="s" r="J535" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
       <c t="s" r="M535" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="536" ht="14.25" customHeight="1">
@@ -19322,13 +19351,13 @@
       </c>
       <c r="D536" s="7"/>
       <c t="s" r="E536" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F536" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G536" s="8">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c t="s" r="H536" s="8">
         <v>57</v>
@@ -19370,7 +19399,7 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
@@ -19385,12 +19414,12 @@
         <v>229</v>
       </c>
       <c t="s" r="J538" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K538" s="7"/>
       <c r="L538" s="7"/>
       <c t="s" r="M538" s="7">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="539" ht="14.25" customHeight="1">
@@ -19405,7 +19434,7 @@
       </c>
       <c r="D539" s="7"/>
       <c t="s" r="E539" s="7">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F539" s="7">
         <v>330</v>
@@ -19414,20 +19443,20 @@
         <v>57</v>
       </c>
       <c t="s" r="H539" s="8">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c t="s" r="I539" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J539" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c t="s" r="K539" s="7">
         <v>66</v>
       </c>
       <c r="L539" s="7"/>
       <c t="s" r="M539" s="7">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="540" ht="15" customHeight="1">
@@ -19442,13 +19471,13 @@
       </c>
       <c r="D540" s="7"/>
       <c t="s" r="E540" s="7">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F540" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G540" s="8">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c t="s" r="H540" s="8">
         <v>57</v>
@@ -19457,7 +19486,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J540" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K540" s="7"/>
       <c r="L540" s="7"/>
@@ -19490,7 +19519,7 @@
       </c>
       <c r="D542" s="7"/>
       <c t="s" r="E542" s="7">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="F542" s="7">
         <v>330</v>
@@ -19499,13 +19528,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H542" s="8">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c t="s" r="I542" s="7">
         <v>149</v>
       </c>
       <c t="s" r="J542" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K542" s="7"/>
       <c r="L542" s="7"/>
@@ -19538,7 +19567,7 @@
       </c>
       <c r="D544" s="7"/>
       <c t="s" r="E544" s="7">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F544" s="7">
         <v>330</v>
@@ -19547,13 +19576,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H544" s="8">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c t="s" r="I544" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c t="s" r="J544" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K544" s="7"/>
       <c r="L544" s="7"/>
@@ -19573,13 +19602,13 @@
       </c>
       <c r="D545" s="7"/>
       <c t="s" r="E545" s="7">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F545" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G545" s="8">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c t="s" r="H545" s="8">
         <v>57</v>
@@ -19588,7 +19617,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J545" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K545" s="7"/>
       <c r="L545" s="7"/>
@@ -19621,7 +19650,7 @@
       </c>
       <c r="D547" s="7"/>
       <c t="s" r="E547" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F547" s="7">
         <v>330</v>
@@ -19630,18 +19659,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H547" s="8">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c t="s" r="I547" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J547" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K547" s="7"/>
       <c r="L547" s="7"/>
       <c t="s" r="M547" s="7">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="548" ht="14.25" customHeight="1">
@@ -19656,13 +19685,13 @@
       </c>
       <c r="D548" s="7"/>
       <c t="s" r="E548" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F548" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G548" s="8">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c t="s" r="H548" s="8">
         <v>17</v>
@@ -19671,7 +19700,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J548" s="7">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="K548" s="7"/>
       <c r="L548" s="7"/>
@@ -19679,7 +19708,7 @@
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c t="s" r="A549" s="9">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B549" s="9"/>
       <c r="C549" s="9"/>
@@ -19699,7 +19728,7 @@
     <row r="550" ht="66" customHeight="1"/>
     <row r="551" ht="16.5" customHeight="1">
       <c t="s" r="A551" s="10">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B551" s="10"/>
       <c r="C551" s="10"/>
@@ -19712,7 +19741,7 @@
       <c r="J551" s="10"/>
       <c r="K551" s="10"/>
       <c t="s" r="L551" s="11">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="M551" s="11"/>
       <c r="N551" s="11"/>

--- a/Data/FlightPlan/FPL_08AUG26.xlsx
+++ b/Data/FlightPlan/FPL_08AUG26.xlsx
@@ -455,690 +455,693 @@
     <t>21:25</t>
   </si>
   <si>
+    <t>21:54</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A525</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>16:12</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:18</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:19</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:41</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>5069 *</t>
+  </si>
+  <si>
+    <t>VN-A537</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>18:03</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>20:26</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:07</t>
+  </si>
+  <si>
+    <t>22:32</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>14:42</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>19:19</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>VN-A550</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>19:09</t>
+  </si>
+  <si>
+    <t>21:23</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>22:13</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>18:54</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:29</t>
+  </si>
+  <si>
+    <t>19:02</t>
+  </si>
+  <si>
+    <t>21:19</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>20:02</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:13</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:47</t>
+  </si>
+  <si>
+    <t>11:39</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>19:17</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
     <t>21:47</t>
   </si>
   <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A525</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>16:12</t>
-  </si>
-  <si>
-    <t>19:21</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:18</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>20:34</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:19</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:41</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>17:32</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>5069 *</t>
-  </si>
-  <si>
-    <t>VN-A537</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>09:11</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:43</t>
-  </si>
-  <si>
-    <t>18:03</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>20:26</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:07</t>
-  </si>
-  <si>
-    <t>22:32</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>14:42</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>19:19</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>VN-A550</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>19:09</t>
-  </si>
-  <si>
-    <t>21:23</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>22:13</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>18:54</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:29</t>
-  </si>
-  <si>
-    <t>19:02</t>
-  </si>
-  <si>
-    <t>21:27</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>10:46</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>14:08</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>20:02</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:13</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:47</t>
-  </si>
-  <si>
-    <t>11:39</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>19:17</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
     <t>VN-A633</t>
   </si>
   <si>
@@ -1214,90 +1217,93 @@
     <t>20:03</t>
   </si>
   <si>
+    <t>22:26</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>20:49</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
+    <t>18:18</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>09:46</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
     <t>22:10</t>
   </si>
   <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>16:24</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>20:49</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>15:46</t>
-  </si>
-  <si>
-    <t>18:18</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>09:46</t>
-  </si>
-  <si>
-    <t>14:46</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
     <t>00:20</t>
   </si>
   <si>
@@ -1325,6 +1331,12 @@
     <t>15:38</t>
   </si>
   <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
     <t>23:30</t>
   </si>
   <si>
@@ -1337,12 +1349,6 @@
     <t>02:00</t>
   </si>
   <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>16:19</t>
-  </si>
-  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1574,6 +1580,9 @@
     <t>14:56</t>
   </si>
   <si>
+    <t>22:37</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1622,7 +1631,7 @@
     <t>13:11</t>
   </si>
   <si>
-    <t>22:09</t>
+    <t>22:27</t>
   </si>
   <si>
     <t>VN-A666</t>
@@ -1727,9 +1736,6 @@
     <t>17:28</t>
   </si>
   <si>
-    <t>21:57</t>
-  </si>
-  <si>
     <t>VN-A673</t>
   </si>
   <si>
@@ -1886,9 +1892,6 @@
     <t>SVO</t>
   </si>
   <si>
-    <t>05:22</t>
-  </si>
-  <si>
     <t>VN-A812</t>
   </si>
   <si>
@@ -1907,7 +1910,7 @@
     <t>SYD</t>
   </si>
   <si>
-    <t>08:07</t>
+    <t>07:39</t>
   </si>
   <si>
     <t>VN-A815</t>
@@ -1925,7 +1928,7 @@
     <t>Total Record(s): 455</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 08, 2026 20:22</t>
+    <t xml:space="preserve">Generated on  Aug 08, 2026 20:34</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -8502,7 +8505,7 @@
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>148</v>
+        <v>376</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8532,7 +8535,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8544,7 +8547,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>165</v>
@@ -8552,7 +8555,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8567,7 +8570,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8587,7 +8590,7 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8602,7 +8605,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8617,7 +8620,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8637,7 +8640,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8674,7 +8677,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8696,7 +8699,7 @@
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8711,7 +8714,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8720,7 +8723,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>199</v>
@@ -8733,7 +8736,7 @@
       </c>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8748,13 +8751,13 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>73</v>
@@ -8800,7 +8803,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8835,7 +8838,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8855,7 +8858,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8870,7 +8873,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8879,7 +8882,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>288</v>
@@ -8890,7 +8893,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8905,13 +8908,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>73</v>
@@ -8940,7 +8943,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8975,7 +8978,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8990,12 +8993,12 @@
         <v>132</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -9010,7 +9013,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -9019,17 +9022,19 @@
         <v>73</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I213" s="7">
         <v>184</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c r="M213" s="7"/>
+      <c t="s" r="M213" s="7">
+        <v>136</v>
+      </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
@@ -9043,19 +9048,19 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>202</v>
@@ -9091,7 +9096,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9111,7 +9116,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9126,7 +9131,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9141,12 +9146,12 @@
         <v>221</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9161,7 +9166,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9173,7 +9178,7 @@
         <v>348</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>301</v>
@@ -9196,7 +9201,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9214,7 +9219,7 @@
         <v>196</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
@@ -9233,7 +9238,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9242,7 +9247,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>198</v>
@@ -9255,7 +9260,7 @@
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9270,13 +9275,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>73</v>
@@ -9292,7 +9297,7 @@
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9307,7 +9312,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9329,7 +9334,7 @@
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9344,7 +9349,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9356,7 +9361,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>31</v>
@@ -9366,7 +9371,7 @@
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9396,7 +9401,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9408,7 +9413,7 @@
         <v>243</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>173</v>
@@ -9431,7 +9436,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9481,7 +9486,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9501,7 +9506,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9516,7 +9521,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9551,7 +9556,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9560,7 +9565,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>331</v>
@@ -9571,7 +9576,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9586,13 +9591,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>73</v>
@@ -9608,7 +9613,7 @@
       </c>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9623,7 +9628,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9645,7 +9650,7 @@
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9660,7 +9665,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9697,7 +9702,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9709,7 +9714,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>304</v>
@@ -9734,7 +9739,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9756,7 +9761,7 @@
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9771,7 +9776,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9783,7 +9788,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>149</v>
@@ -9793,7 +9798,7 @@
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9823,7 +9828,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9835,10 +9840,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9858,7 +9863,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9878,7 +9883,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9893,7 +9898,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9902,7 +9907,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>301</v>
@@ -9928,13 +9933,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>57</v>
@@ -9948,7 +9953,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9963,7 +9968,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9972,7 +9977,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>103</v>
@@ -9983,7 +9988,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9998,19 +10003,19 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>178</v>
@@ -10046,7 +10051,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -10066,7 +10071,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10081,7 +10086,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -10093,10 +10098,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -10116,7 +10121,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10136,7 +10141,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10151,7 +10156,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10171,7 +10176,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10201,7 +10206,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10221,7 +10226,7 @@
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10236,7 +10241,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10248,7 +10253,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>370</v>
@@ -10271,7 +10276,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10291,7 +10296,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10306,7 +10311,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10341,7 +10346,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10350,7 +10355,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>67</v>
@@ -10363,7 +10368,7 @@
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10378,13 +10383,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>17</v>
@@ -10400,7 +10405,7 @@
       </c>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>136</v>
+        <v>430</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10415,7 +10420,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10427,10 +10432,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c t="s" r="K256" s="7">
         <v>50</v>
@@ -10467,7 +10472,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10476,10 +10481,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>86</v>
@@ -10487,7 +10492,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10502,13 +10507,13 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>17</v>
@@ -10522,7 +10527,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10537,7 +10542,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10546,20 +10551,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c t="s" r="K260" s="7">
         <v>158</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10574,29 +10579,29 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="K261" s="7">
         <v>211</v>
       </c>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10611,7 +10616,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10620,7 +10625,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>24</v>
@@ -10646,13 +10651,13 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
@@ -10676,14 +10681,14 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10692,20 +10697,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>131</v>
+        <v>387</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>402</v>
+        <v>147</v>
       </c>
       <c t="s" r="K264" s="7">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>438</v>
+        <v>324</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10713,36 +10718,36 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>131</v>
+        <v>387</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>295</v>
+        <v>420</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>439</v>
+        <v>50</v>
       </c>
       <c t="s" r="K265" s="7">
-        <v>440</v>
+        <v>51</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>441</v>
+        <v>149</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10772,7 +10777,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10792,7 +10797,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10807,7 +10812,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10842,7 +10847,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10862,7 +10867,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10877,7 +10882,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10897,7 +10902,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10912,7 +10917,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10940,14 +10945,14 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10956,20 +10961,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>386</v>
+        <v>131</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>147</v>
+        <v>403</v>
       </c>
       <c t="s" r="K272" s="7">
-        <v>391</v>
+        <v>179</v>
       </c>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>49</v>
+        <v>442</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10977,36 +10982,36 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>386</v>
+        <v>131</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>419</v>
+        <v>295</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>50</v>
+        <v>443</v>
       </c>
       <c t="s" r="K273" s="7">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>403</v>
+        <v>445</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -11036,7 +11041,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -11056,7 +11061,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -11071,7 +11076,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -11106,7 +11111,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -11115,7 +11120,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>194</v>
@@ -11126,7 +11131,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11141,13 +11146,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>17</v>
@@ -11161,7 +11166,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11176,7 +11181,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11188,7 +11193,7 @@
         <v>278</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>26</v>
@@ -11196,7 +11201,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11211,7 +11216,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11226,12 +11231,12 @@
         <v>133</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11261,7 +11266,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11281,7 +11286,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11296,7 +11301,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11316,7 +11321,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11331,7 +11336,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11351,7 +11356,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11366,7 +11371,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11421,7 +11426,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11436,7 +11441,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11484,7 +11489,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11504,7 +11509,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11519,7 +11524,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11528,7 +11533,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>199</v>
@@ -11539,7 +11544,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11554,19 +11559,19 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>54</v>
@@ -11602,7 +11607,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11614,7 +11619,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>316</v>
@@ -11637,7 +11642,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11657,7 +11662,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11672,7 +11677,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11692,7 +11697,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11707,7 +11712,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11727,7 +11732,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11742,7 +11747,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11754,7 +11759,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>227</v>
@@ -11779,7 +11784,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11791,13 +11796,13 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c t="s" r="K298" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
@@ -11831,7 +11836,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11868,7 +11873,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11886,11 +11891,11 @@
         <v>170</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11905,7 +11910,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11927,7 +11932,7 @@
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11942,7 +11947,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11960,7 +11965,7 @@
         <v>295</v>
       </c>
       <c t="s" r="K303" s="7">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
@@ -11994,7 +11999,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -12006,15 +12011,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -12029,7 +12034,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -12064,7 +12069,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -12079,12 +12084,12 @@
         <v>360</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -12099,7 +12104,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -12134,7 +12139,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12154,7 +12159,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12169,7 +12174,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -12189,7 +12194,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -12204,7 +12209,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12226,7 +12231,7 @@
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12241,7 +12246,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -12263,7 +12268,7 @@
       </c>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12293,7 +12298,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12313,7 +12318,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12328,7 +12333,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12348,7 +12353,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12363,7 +12368,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12372,7 +12377,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>316</v>
@@ -12383,7 +12388,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12398,29 +12403,29 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>370</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12435,7 +12440,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12444,7 +12449,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>338</v>
@@ -12457,7 +12462,7 @@
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12472,13 +12477,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
@@ -12494,7 +12499,7 @@
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12509,7 +12514,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12546,7 +12551,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12564,7 +12569,7 @@
         <v>46</v>
       </c>
       <c t="s" r="K321" s="7">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
@@ -12583,7 +12588,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12598,7 +12603,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12616,7 +12621,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12631,7 +12636,7 @@
         <v>241</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12664,7 +12669,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12673,7 +12678,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>208</v>
@@ -12684,7 +12689,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12699,19 +12704,19 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>316</v>
@@ -12719,7 +12724,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12734,7 +12739,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12743,7 +12748,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>18</v>
@@ -12754,7 +12759,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12769,13 +12774,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>17</v>
@@ -12804,7 +12809,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12826,7 +12831,7 @@
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12841,7 +12846,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12863,7 +12868,7 @@
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12878,7 +12883,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12900,7 +12905,7 @@
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>476</v>
+        <v>83</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12915,7 +12920,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12933,11 +12938,11 @@
         <v>238</v>
       </c>
       <c t="s" r="K332" s="7">
-        <v>186</v>
+        <v>420</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>178</v>
+        <v>50</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12952,7 +12957,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12964,17 +12969,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>335</v>
       </c>
       <c t="s" r="K333" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -13004,7 +13009,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -13016,7 +13021,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>219</v>
@@ -13024,7 +13029,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -13039,7 +13044,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -13074,7 +13079,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -13094,7 +13099,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -13109,7 +13114,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -13129,7 +13134,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13144,7 +13149,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -13192,7 +13197,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13212,7 +13217,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13227,7 +13232,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13247,7 +13252,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13262,7 +13267,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -13282,7 +13287,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13297,7 +13302,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -13317,7 +13322,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13332,7 +13337,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13367,7 +13372,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13387,7 +13392,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13402,7 +13407,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13450,7 +13455,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13465,12 +13470,12 @@
         <v>95</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13485,7 +13490,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13505,7 +13510,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13520,7 +13525,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13532,7 +13537,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>161</v>
@@ -13555,7 +13560,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13575,7 +13580,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13590,7 +13595,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13599,7 +13604,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>353</v>
@@ -13610,7 +13615,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13625,13 +13630,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>73</v>
@@ -13640,14 +13645,14 @@
         <v>67</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="K354" s="7">
         <v>80</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13662,7 +13667,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13671,20 +13676,20 @@
         <v>73</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c t="s" r="K355" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13699,13 +13704,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>73</v>
@@ -13714,14 +13719,14 @@
         <v>92</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c t="s" r="K356" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13751,7 +13756,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13766,7 +13771,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13786,7 +13791,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13795,7 +13800,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>316</v>
@@ -13806,7 +13811,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13821,27 +13826,27 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13856,7 +13861,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13891,7 +13896,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13903,7 +13908,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>215</v>
@@ -13926,7 +13931,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13935,7 +13940,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>258</v>
@@ -13948,7 +13953,7 @@
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>186</v>
+        <v>147</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13963,13 +13968,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>17</v>
@@ -13981,11 +13986,11 @@
         <v>83</v>
       </c>
       <c t="s" r="K364" s="7">
-        <v>266</v>
+        <v>420</v>
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>401</v>
+        <v>50</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -14015,7 +14020,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -14035,7 +14040,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -14050,7 +14055,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -14070,7 +14075,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -14085,7 +14090,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -14097,7 +14102,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>183</v>
@@ -14105,7 +14110,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -14120,7 +14125,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -14140,7 +14145,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -14155,7 +14160,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -14192,7 +14197,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -14214,7 +14219,7 @@
       </c>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>178</v>
+        <v>523</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14244,7 +14249,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14264,7 +14269,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14279,7 +14284,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14299,7 +14304,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14314,7 +14319,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14329,7 +14334,7 @@
         <v>331</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -14349,7 +14354,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -14369,7 +14374,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14384,7 +14389,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14404,7 +14409,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14419,7 +14424,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14439,7 +14444,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14454,7 +14459,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14463,13 +14468,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>324</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -14487,22 +14492,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -14535,7 +14540,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14547,15 +14552,15 @@
         <v>189</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14570,7 +14575,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -14590,7 +14595,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14605,7 +14610,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -14640,7 +14645,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14675,7 +14680,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -14690,7 +14695,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c t="s" r="K386" s="7">
         <v>82</v>
@@ -14712,7 +14717,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14764,7 +14769,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14773,10 +14778,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>165</v>
@@ -14784,7 +14789,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14799,13 +14804,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>17</v>
@@ -14819,7 +14824,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14834,7 +14839,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14843,18 +14848,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>331</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14869,13 +14874,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
@@ -14887,11 +14892,11 @@
         <v>161</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14906,7 +14911,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14928,7 +14933,7 @@
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14943,7 +14948,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14980,7 +14985,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -15002,7 +15007,7 @@
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -15032,7 +15037,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -15067,7 +15072,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -15087,7 +15092,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -15102,7 +15107,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -15111,7 +15116,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>20</v>
@@ -15124,7 +15129,7 @@
       </c>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -15139,13 +15144,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>73</v>
@@ -15161,7 +15166,7 @@
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -15176,7 +15181,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -15191,7 +15196,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -15209,7 +15214,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -15221,7 +15226,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>279</v>
@@ -15257,7 +15262,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15277,7 +15282,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15292,7 +15297,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15307,12 +15312,12 @@
         <v>139</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15327,7 +15332,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15347,7 +15352,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15362,7 +15367,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -15384,7 +15389,7 @@
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15414,7 +15419,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -15449,7 +15454,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -15469,7 +15474,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15484,7 +15489,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15519,7 +15524,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -15541,7 +15546,7 @@
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15556,7 +15561,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15565,7 +15570,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>237</v>
@@ -15591,13 +15596,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>17</v>
@@ -15606,7 +15611,7 @@
         <v>252</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -15639,7 +15644,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15659,7 +15664,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15674,7 +15679,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15694,7 +15699,7 @@
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15709,7 +15714,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15724,12 +15729,12 @@
         <v>288</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15744,7 +15749,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -15779,7 +15784,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -15814,7 +15819,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15834,7 +15839,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15849,7 +15854,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15858,10 +15863,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>18</v>
@@ -15897,7 +15902,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15932,7 +15937,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15947,14 +15952,14 @@
         <v>232</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c t="s" r="K425" s="7">
         <v>183</v>
       </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15969,7 +15974,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15989,7 +15994,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -16004,7 +16009,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -16016,7 +16021,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>108</v>
@@ -16024,7 +16029,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -16039,7 +16044,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -16048,7 +16053,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>202</v>
@@ -16072,22 +16077,22 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -16120,7 +16125,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -16140,7 +16145,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -16155,7 +16160,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -16167,7 +16172,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>19</v>
@@ -16175,7 +16180,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -16190,7 +16195,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -16199,7 +16204,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>43</v>
@@ -16210,7 +16215,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -16225,13 +16230,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>17</v>
@@ -16260,7 +16265,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -16280,7 +16285,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -16295,7 +16300,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F436" s="7">
         <v>320</v>
@@ -16343,7 +16348,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -16363,7 +16368,7 @@
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -16378,7 +16383,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -16413,7 +16418,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -16422,7 +16427,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>226</v>
@@ -16433,7 +16438,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16448,13 +16453,13 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>17</v>
@@ -16483,7 +16488,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -16503,7 +16508,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>572</v>
+        <v>403</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16533,7 +16538,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -16548,7 +16553,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -16568,7 +16573,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16603,7 +16608,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16625,7 +16630,7 @@
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16640,7 +16645,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -16692,7 +16697,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -16727,7 +16732,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -16775,7 +16780,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16790,12 +16795,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16810,7 +16815,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16830,7 +16835,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16845,7 +16850,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16857,7 +16862,7 @@
         <v>142</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>210</v>
@@ -16865,7 +16870,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16880,7 +16885,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16892,7 +16897,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>128</v>
@@ -16900,7 +16905,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16915,7 +16920,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -16950,7 +16955,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16965,12 +16970,12 @@
         <v>117</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16985,7 +16990,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
@@ -17000,12 +17005,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -17020,7 +17025,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -17068,7 +17073,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -17088,7 +17093,7 @@
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
       <c t="s" r="M461" s="7">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
@@ -17103,7 +17108,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
@@ -17123,7 +17128,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -17138,7 +17143,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F463" s="7">
         <v>320</v>
@@ -17150,10 +17155,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -17173,7 +17178,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F464" s="7">
         <v>320</v>
@@ -17191,11 +17196,11 @@
         <v>347</v>
       </c>
       <c t="s" r="K464" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -17210,7 +17215,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F465" s="7">
         <v>320</v>
@@ -17222,7 +17227,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>129</v>
@@ -17232,7 +17237,7 @@
       </c>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -17247,7 +17252,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F466" s="7">
         <v>320</v>
@@ -17262,7 +17267,7 @@
         <v>249</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c t="s" r="K466" s="7">
         <v>133</v>
@@ -17284,7 +17289,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F467" s="7">
         <v>320</v>
@@ -17296,10 +17301,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c t="s" r="K467" s="7">
         <v>266</v>
@@ -17336,7 +17341,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -17348,7 +17353,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>221</v>
@@ -17356,7 +17361,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -17371,7 +17376,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -17391,7 +17396,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17406,7 +17411,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -17418,13 +17423,13 @@
         <v>57</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>244</v>
       </c>
       <c t="s" r="K471" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
@@ -17443,7 +17448,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -17461,11 +17466,11 @@
         <v>20</v>
       </c>
       <c t="s" r="K472" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -17480,7 +17485,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
@@ -17517,7 +17522,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -17535,11 +17540,11 @@
         <v>258</v>
       </c>
       <c t="s" r="K474" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -17554,7 +17559,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -17587,7 +17592,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
@@ -17599,7 +17604,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="J476" s="7">
         <v>152</v>
@@ -17635,7 +17640,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -17670,7 +17675,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -17690,7 +17695,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17705,7 +17710,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -17740,7 +17745,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -17775,7 +17780,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -17795,7 +17800,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17810,7 +17815,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -17825,7 +17830,7 @@
         <v>375</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
@@ -17843,7 +17848,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
@@ -17891,7 +17896,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -17911,7 +17916,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -17926,7 +17931,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
@@ -17941,7 +17946,7 @@
         <v>223</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -17961,7 +17966,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -17981,7 +17986,7 @@
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -17996,7 +18001,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
@@ -18011,10 +18016,10 @@
         <v>144</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c t="s" r="K489" s="7">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
@@ -18033,7 +18038,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -18048,7 +18053,7 @@
         <v>266</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c t="s" r="K490" s="7">
         <v>239</v>
@@ -18085,7 +18090,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -18100,12 +18105,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
       <c t="s" r="M492" s="7">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -18120,7 +18125,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
@@ -18129,10 +18134,10 @@
         <v>131</v>
       </c>
       <c t="s" r="H493" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c t="s" r="J493" s="7">
         <v>248</v>
@@ -18155,13 +18160,13 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G494" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H494" s="8">
         <v>131</v>
@@ -18175,7 +18180,7 @@
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -18190,7 +18195,7 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F495" s="7">
         <v>321</v>
@@ -18210,7 +18215,7 @@
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
       <c t="s" r="M495" s="7">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="496" ht="14.25" customHeight="1">
@@ -18225,7 +18230,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F496" s="7">
         <v>321</v>
@@ -18237,7 +18242,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="J496" s="7">
         <v>238</v>
@@ -18258,7 +18263,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F497" s="7">
         <v>321</v>
@@ -18306,7 +18311,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -18341,7 +18346,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F500" s="7">
         <v>320</v>
@@ -18356,7 +18361,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J500" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
@@ -18376,7 +18381,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F501" s="7">
         <v>320</v>
@@ -18396,7 +18401,7 @@
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
       <c t="s" r="M501" s="7">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="502" ht="14.25" customHeight="1">
@@ -18411,7 +18416,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F502" s="7">
         <v>320</v>
@@ -18431,7 +18436,7 @@
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
       <c t="s" r="M502" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="503" ht="14.25" customHeight="1">
@@ -18446,7 +18451,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -18461,12 +18466,12 @@
         <v>103</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
       <c t="s" r="M503" s="7">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="504" ht="14.25" customHeight="1">
@@ -18481,7 +18486,7 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F504" s="7">
         <v>320</v>
@@ -18529,7 +18534,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -18564,7 +18569,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F507" s="7">
         <v>321</v>
@@ -18584,7 +18589,7 @@
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
       <c t="s" r="M507" s="7">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="508" ht="14.25" customHeight="1">
@@ -18599,7 +18604,7 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F508" s="7">
         <v>321</v>
@@ -18608,7 +18613,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H508" s="8">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c t="s" r="I508" s="7">
         <v>133</v>
@@ -18636,13 +18641,13 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F509" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G509" s="8">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c t="s" r="H509" s="8">
         <v>17</v>
@@ -18688,7 +18693,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F511" s="7">
         <v>321</v>
@@ -18700,7 +18705,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c t="s" r="J511" s="7">
         <v>150</v>
@@ -18708,7 +18713,7 @@
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
       <c t="s" r="M511" s="7">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="512" ht="14.25" customHeight="1">
@@ -18723,7 +18728,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F512" s="7">
         <v>321</v>
@@ -18738,12 +18743,12 @@
         <v>194</v>
       </c>
       <c t="s" r="J512" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
       <c t="s" r="M512" s="7">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="513" ht="14.25" customHeight="1">
@@ -18758,7 +18763,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F513" s="7">
         <v>321</v>
@@ -18778,7 +18783,7 @@
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
       <c t="s" r="M513" s="7">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="514" ht="14.25" customHeight="1">
@@ -18793,7 +18798,7 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F514" s="7">
         <v>321</v>
@@ -18841,7 +18846,7 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F516" s="7">
         <v>321</v>
@@ -18861,7 +18866,7 @@
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
       <c t="s" r="M516" s="7">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -18876,7 +18881,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F517" s="7">
         <v>321</v>
@@ -18896,7 +18901,7 @@
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -18911,7 +18916,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F518" s="7">
         <v>321</v>
@@ -18946,7 +18951,7 @@
       </c>
       <c r="D519" s="7"/>
       <c t="s" r="E519" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F519" s="7">
         <v>321</v>
@@ -18966,7 +18971,7 @@
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
       <c t="s" r="M519" s="7">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="520" ht="15" customHeight="1">
@@ -18981,7 +18986,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F520" s="7">
         <v>321</v>
@@ -19003,7 +19008,7 @@
       </c>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>313</v>
+        <v>179</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -19018,7 +19023,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F521" s="7">
         <v>321</v>
@@ -19070,7 +19075,7 @@
       </c>
       <c r="D523" s="7"/>
       <c t="s" r="E523" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F523" s="7">
         <v>320</v>
@@ -19090,7 +19095,7 @@
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
       <c t="s" r="M523" s="7">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="524" ht="14.25" customHeight="1">
@@ -19105,7 +19110,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F524" s="7">
         <v>320</v>
@@ -19120,7 +19125,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J524" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
@@ -19140,7 +19145,7 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F525" s="7">
         <v>320</v>
@@ -19160,7 +19165,7 @@
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
       <c t="s" r="M525" s="7">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="526" ht="14.25" customHeight="1">
@@ -19175,7 +19180,7 @@
       </c>
       <c r="D526" s="7"/>
       <c t="s" r="E526" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F526" s="7">
         <v>320</v>
@@ -19210,7 +19215,7 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F527" s="7">
         <v>320</v>
@@ -19230,7 +19235,7 @@
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
       <c t="s" r="M527" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="528" ht="14.25" customHeight="1">
@@ -19245,7 +19250,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F528" s="7">
         <v>320</v>
@@ -19260,7 +19265,7 @@
         <v>364</v>
       </c>
       <c t="s" r="J528" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
@@ -19293,7 +19298,7 @@
       </c>
       <c r="D530" s="7"/>
       <c t="s" r="E530" s="7">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F530" s="7">
         <v>330</v>
@@ -19313,7 +19318,7 @@
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
       <c t="s" r="M530" s="7">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="531" ht="14.25" customHeight="1">
@@ -19328,7 +19333,7 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
@@ -19337,20 +19342,20 @@
         <v>57</v>
       </c>
       <c t="s" r="H531" s="8">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c t="s" r="I531" s="7">
         <v>265</v>
       </c>
       <c t="s" r="J531" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="K531" s="7">
         <v>24</v>
       </c>
       <c r="L531" s="7"/>
       <c t="s" r="M531" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="532" ht="14.25" customHeight="1">
@@ -19365,13 +19370,13 @@
       </c>
       <c r="D532" s="7"/>
       <c t="s" r="E532" s="7">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F532" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G532" s="8">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c t="s" r="H532" s="8">
         <v>57</v>
@@ -19413,7 +19418,7 @@
       </c>
       <c r="D534" s="7"/>
       <c t="s" r="E534" s="7">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F534" s="7">
         <v>330</v>
@@ -19422,18 +19427,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H534" s="8">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c t="s" r="I534" s="7">
         <v>219</v>
       </c>
       <c t="s" r="J534" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K534" s="7"/>
       <c r="L534" s="7"/>
       <c t="s" r="M534" s="7">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="535" ht="15" customHeight="1">
@@ -19448,13 +19453,13 @@
       </c>
       <c r="D535" s="7"/>
       <c t="s" r="E535" s="7">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F535" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G535" s="8">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c t="s" r="H535" s="8">
         <v>57</v>
@@ -19468,7 +19473,7 @@
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
       <c t="s" r="M535" s="7">
-        <v>625</v>
+        <v>378</v>
       </c>
     </row>
     <row r="536" ht="14.25" customHeight="1">
@@ -19498,7 +19503,7 @@
       </c>
       <c r="D537" s="7"/>
       <c t="s" r="E537" s="7">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F537" s="7">
         <v>330</v>
@@ -19518,7 +19523,7 @@
       <c r="K537" s="7"/>
       <c r="L537" s="7"/>
       <c t="s" r="M537" s="7">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="538" ht="14.25" customHeight="1">
@@ -19533,7 +19538,7 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
@@ -19542,7 +19547,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H538" s="8">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c t="s" r="I538" s="7">
         <v>353</v>
@@ -19555,7 +19560,7 @@
       </c>
       <c r="L538" s="7"/>
       <c t="s" r="M538" s="7">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="539" ht="14.25" customHeight="1">
@@ -19570,13 +19575,13 @@
       </c>
       <c r="D539" s="7"/>
       <c t="s" r="E539" s="7">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F539" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G539" s="8">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c t="s" r="H539" s="8">
         <v>57</v>
@@ -19585,7 +19590,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J539" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K539" s="7"/>
       <c r="L539" s="7"/>
@@ -19618,7 +19623,7 @@
       </c>
       <c r="D541" s="7"/>
       <c t="s" r="E541" s="7">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F541" s="7">
         <v>330</v>
@@ -19627,7 +19632,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H541" s="8">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c t="s" r="I541" s="7">
         <v>146</v>
@@ -19638,7 +19643,7 @@
       <c r="K541" s="7"/>
       <c r="L541" s="7"/>
       <c t="s" r="M541" s="7">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="542" ht="14.25" customHeight="1">
@@ -19668,7 +19673,7 @@
       </c>
       <c r="D543" s="7"/>
       <c t="s" r="E543" s="7">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F543" s="7">
         <v>330</v>
@@ -19677,10 +19682,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H543" s="8">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c t="s" r="I543" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c t="s" r="J543" s="7">
         <v>322</v>
@@ -19703,13 +19708,13 @@
       </c>
       <c r="D544" s="7"/>
       <c t="s" r="E544" s="7">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F544" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G544" s="8">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c t="s" r="H544" s="8">
         <v>57</v>
@@ -19718,7 +19723,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J544" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K544" s="7"/>
       <c r="L544" s="7"/>
@@ -19751,7 +19756,7 @@
       </c>
       <c r="D546" s="7"/>
       <c t="s" r="E546" s="7">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F546" s="7">
         <v>330</v>
@@ -19760,7 +19765,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H546" s="8">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c t="s" r="I546" s="7">
         <v>41</v>
@@ -19771,7 +19776,7 @@
       <c r="K546" s="7"/>
       <c r="L546" s="7"/>
       <c t="s" r="M546" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="547" ht="14.25" customHeight="1">
@@ -19786,22 +19791,22 @@
       </c>
       <c r="D547" s="7"/>
       <c t="s" r="E547" s="7">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F547" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G547" s="8">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c t="s" r="H547" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I547" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c t="s" r="J547" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K547" s="7"/>
       <c r="L547" s="7"/>
@@ -19809,7 +19814,7 @@
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c t="s" r="A548" s="9">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B548" s="9"/>
       <c r="C548" s="9"/>
@@ -19829,7 +19834,7 @@
     <row r="549" ht="65.25" customHeight="1"/>
     <row r="550" ht="17.25" customHeight="1">
       <c t="s" r="A550" s="10">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B550" s="10"/>
       <c r="C550" s="10"/>
@@ -19842,7 +19847,7 @@
       <c r="J550" s="10"/>
       <c r="K550" s="10"/>
       <c t="s" r="L550" s="11">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M550" s="11"/>
       <c r="N550" s="11"/>
